--- a/src/node/uploads/blue.xlsx
+++ b/src/node/uploads/blue.xlsx
@@ -5142,7 +5142,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1327"/>
+  <dimension ref="A1:B1320"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="35.25" customWidth="1"/>
@@ -15708,41 +15708,6 @@
         <v>64.67152752</v>
       </c>
     </row>
-    <row r="1321" spans="2:2">
-      <c r="B1321">
-        <v>65.08570912</v>
-      </c>
-    </row>
-    <row r="1322" spans="2:2">
-      <c r="B1322">
-        <v>64.17519281</v>
-      </c>
-    </row>
-    <row r="1323" spans="2:2">
-      <c r="B1323">
-        <v>65.09333606</v>
-      </c>
-    </row>
-    <row r="1324" spans="2:2">
-      <c r="B1324">
-        <v>64.74690188</v>
-      </c>
-    </row>
-    <row r="1325" spans="2:2">
-      <c r="B1325">
-        <v>65.90535917</v>
-      </c>
-    </row>
-    <row r="1326" spans="2:2">
-      <c r="B1326">
-        <v>66.46568024</v>
-      </c>
-    </row>
-    <row r="1327" spans="2:2">
-      <c r="B1327">
-        <v>66.13690536</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/src/node/uploads/blue.xlsx
+++ b/src/node/uploads/blue.xlsx
@@ -5142,7 +5142,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1320"/>
+  <dimension ref="A1:B1327"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="35.25" customWidth="1"/>
@@ -15708,6 +15708,41 @@
         <v>64.67152752</v>
       </c>
     </row>
+    <row r="1321" spans="2:2">
+      <c r="B1321">
+        <v>65.08570912</v>
+      </c>
+    </row>
+    <row r="1322" spans="2:2">
+      <c r="B1322">
+        <v>64.17519281</v>
+      </c>
+    </row>
+    <row r="1323" spans="2:2">
+      <c r="B1323">
+        <v>65.09333606</v>
+      </c>
+    </row>
+    <row r="1324" spans="2:2">
+      <c r="B1324">
+        <v>64.74690188</v>
+      </c>
+    </row>
+    <row r="1325" spans="2:2">
+      <c r="B1325">
+        <v>65.90535917</v>
+      </c>
+    </row>
+    <row r="1326" spans="2:2">
+      <c r="B1326">
+        <v>66.46568024</v>
+      </c>
+    </row>
+    <row r="1327" spans="2:2">
+      <c r="B1327">
+        <v>66.13690536</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
